--- a/data.mn/public/datasets/household-expenditure-by-location.xlsx
+++ b/data.mn/public/datasets/household-expenditure-by-location.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,414 +414,888 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>year</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1998</v>
-      </c>
-      <c r="D1" t="n">
-        <v>1999</v>
-      </c>
-      <c r="E1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2003</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J1" t="n">
-        <v>2005</v>
-      </c>
-      <c r="K1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="L1" t="n">
-        <v>2007</v>
-      </c>
-      <c r="M1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="N1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="O1" t="n">
-        <v>2010</v>
-      </c>
-      <c r="P1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="R1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="S1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="T1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="U1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="V1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="W1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>National</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="n">
-        <v>69098</v>
-      </c>
-      <c r="D2" t="n">
-        <v>71804</v>
-      </c>
-      <c r="E2" t="n">
-        <v>108011</v>
-      </c>
-      <c r="F2" t="n">
-        <v>111119</v>
-      </c>
-      <c r="G2" t="n">
-        <v>163654</v>
-      </c>
-      <c r="H2" t="n">
-        <v>165552</v>
-      </c>
-      <c r="I2" t="n">
-        <v>182630</v>
-      </c>
-      <c r="J2" t="n">
-        <v>194078</v>
-      </c>
-      <c r="K2" t="n">
-        <v>228172</v>
-      </c>
-      <c r="L2" t="n">
-        <v>292488</v>
-      </c>
-      <c r="M2" t="n">
-        <v>367466</v>
-      </c>
-      <c r="N2" t="n">
-        <v>437602</v>
-      </c>
-      <c r="O2" t="n">
-        <v>450206</v>
-      </c>
-      <c r="P2" t="n">
-        <v>577406</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>820263</v>
-      </c>
-      <c r="R2" t="n">
-        <v>961677</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1076557</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1064808</v>
-      </c>
-      <c r="U2" t="n">
-        <v>966197</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1092384</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1240731</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1416640</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1519398</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1499180</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1851637</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2196615</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2638159</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3141317</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56311</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50401</v>
+      </c>
+      <c r="D2" t="n">
+        <v>61989</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1998</v>
+      </c>
       <c r="B3" t="n">
+        <v>69098</v>
+      </c>
+      <c r="C3" t="n">
+        <v>57083</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80189</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B4" t="n">
+        <v>71804</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59439</v>
+      </c>
+      <c r="D4" t="n">
+        <v>84158</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108011</v>
+      </c>
+      <c r="C5" t="n">
+        <v>102666</v>
+      </c>
+      <c r="D5" t="n">
+        <v>113644</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111119</v>
+      </c>
+      <c r="C6" t="n">
+        <v>85994</v>
+      </c>
+      <c r="D6" t="n">
+        <v>133579</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>163654</v>
+      </c>
+      <c r="C7" t="n">
+        <v>151101</v>
+      </c>
+      <c r="D7" t="n">
+        <v>174847</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>165552</v>
+      </c>
+      <c r="C8" t="n">
+        <v>158021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>173493</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>182630</v>
+      </c>
+      <c r="C9" t="n">
+        <v>186250</v>
+      </c>
+      <c r="D9" t="n">
+        <v>180291</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>194078</v>
+      </c>
+      <c r="C10" t="n">
+        <v>162479</v>
+      </c>
+      <c r="D10" t="n">
+        <v>205109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>228172</v>
+      </c>
+      <c r="C11" t="n">
+        <v>211644</v>
+      </c>
+      <c r="D11" t="n">
+        <v>232188</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>292488</v>
+      </c>
+      <c r="C12" t="n">
+        <v>266768</v>
+      </c>
+      <c r="D12" t="n">
+        <v>308016</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>367466</v>
+      </c>
+      <c r="C13" t="n">
+        <v>293653</v>
+      </c>
+      <c r="D13" t="n">
+        <v>421924</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>437602</v>
+      </c>
+      <c r="C14" t="n">
+        <v>391883</v>
+      </c>
+      <c r="D14" t="n">
+        <v>471336</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>450206</v>
+      </c>
+      <c r="C15" t="n">
+        <v>387937</v>
+      </c>
+      <c r="D15" t="n">
+        <v>501042</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="n">
+        <v>577406</v>
+      </c>
+      <c r="C16" t="n">
+        <v>497633</v>
+      </c>
+      <c r="D16" t="n">
+        <v>648829</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>820263</v>
+      </c>
+      <c r="C17" t="n">
+        <v>657836</v>
+      </c>
+      <c r="D17" t="n">
+        <v>905269</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="n">
+        <v>961677</v>
+      </c>
+      <c r="C18" t="n">
+        <v>833997</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1036809</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1076557</v>
+      </c>
+      <c r="C19" t="n">
+        <v>955939</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1145363</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1064808</v>
+      </c>
+      <c r="C20" t="n">
+        <v>999615</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1100058</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>966197</v>
+      </c>
+      <c r="C21" t="n">
+        <v>889681</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1003893</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1092384</v>
+      </c>
+      <c r="C22" t="n">
+        <v>986406</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1150764</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1240731</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1096030</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1320376</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1416640</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1299329</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1476833</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1519398</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1344028</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1610308</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1499180</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1410755</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1545828</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1851637</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1687923</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1935522</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2196615</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1933596</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2314620</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2638159</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2245940</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2824079</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3141317</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2737181</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3326146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Улсын дүн</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Хот</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Хөдөө</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56311</v>
+      </c>
+      <c r="C2" t="n">
         <v>61989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50401</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B3" t="n">
+        <v>69098</v>
       </c>
       <c r="C3" t="n">
         <v>80189</v>
       </c>
       <c r="D3" t="n">
+        <v>57083</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B4" t="n">
+        <v>71804</v>
+      </c>
+      <c r="C4" t="n">
         <v>84158</v>
-      </c>
-      <c r="E3" t="n">
-        <v>113644</v>
-      </c>
-      <c r="F3" t="n">
-        <v>133579</v>
-      </c>
-      <c r="G3" t="n">
-        <v>174847</v>
-      </c>
-      <c r="H3" t="n">
-        <v>173493</v>
-      </c>
-      <c r="I3" t="n">
-        <v>180291</v>
-      </c>
-      <c r="J3" t="n">
-        <v>205109</v>
-      </c>
-      <c r="K3" t="n">
-        <v>232188</v>
-      </c>
-      <c r="L3" t="n">
-        <v>308016</v>
-      </c>
-      <c r="M3" t="n">
-        <v>421924</v>
-      </c>
-      <c r="N3" t="n">
-        <v>471336</v>
-      </c>
-      <c r="O3" t="n">
-        <v>501042</v>
-      </c>
-      <c r="P3" t="n">
-        <v>648829</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>905269</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1036809</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1145363</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1100058</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1003893</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1150764</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1320376</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1476833</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1610308</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1545828</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1935522</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2314620</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2824079</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3326146</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>50401</v>
-      </c>
-      <c r="C4" t="n">
-        <v>57083</v>
       </c>
       <c r="D4" t="n">
         <v>59439</v>
       </c>
-      <c r="E4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108011</v>
+      </c>
+      <c r="C5" t="n">
+        <v>113644</v>
+      </c>
+      <c r="D5" t="n">
         <v>102666</v>
       </c>
-      <c r="F4" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111119</v>
+      </c>
+      <c r="C6" t="n">
+        <v>133579</v>
+      </c>
+      <c r="D6" t="n">
         <v>85994</v>
       </c>
-      <c r="G4" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>163654</v>
+      </c>
+      <c r="C7" t="n">
+        <v>174847</v>
+      </c>
+      <c r="D7" t="n">
         <v>151101</v>
       </c>
-      <c r="H4" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>165552</v>
+      </c>
+      <c r="C8" t="n">
+        <v>173493</v>
+      </c>
+      <c r="D8" t="n">
         <v>158021</v>
       </c>
-      <c r="I4" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>182630</v>
+      </c>
+      <c r="C9" t="n">
+        <v>180291</v>
+      </c>
+      <c r="D9" t="n">
         <v>186250</v>
       </c>
-      <c r="J4" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>194078</v>
+      </c>
+      <c r="C10" t="n">
+        <v>205109</v>
+      </c>
+      <c r="D10" t="n">
         <v>162479</v>
       </c>
-      <c r="K4" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>228172</v>
+      </c>
+      <c r="C11" t="n">
+        <v>232188</v>
+      </c>
+      <c r="D11" t="n">
         <v>211644</v>
       </c>
-      <c r="L4" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>292488</v>
+      </c>
+      <c r="C12" t="n">
+        <v>308016</v>
+      </c>
+      <c r="D12" t="n">
         <v>266768</v>
       </c>
-      <c r="M4" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>367466</v>
+      </c>
+      <c r="C13" t="n">
+        <v>421924</v>
+      </c>
+      <c r="D13" t="n">
         <v>293653</v>
       </c>
-      <c r="N4" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>437602</v>
+      </c>
+      <c r="C14" t="n">
+        <v>471336</v>
+      </c>
+      <c r="D14" t="n">
         <v>391883</v>
       </c>
-      <c r="O4" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>450206</v>
+      </c>
+      <c r="C15" t="n">
+        <v>501042</v>
+      </c>
+      <c r="D15" t="n">
         <v>387937</v>
       </c>
-      <c r="P4" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="n">
+        <v>577406</v>
+      </c>
+      <c r="C16" t="n">
+        <v>648829</v>
+      </c>
+      <c r="D16" t="n">
         <v>497633</v>
       </c>
-      <c r="Q4" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>820263</v>
+      </c>
+      <c r="C17" t="n">
+        <v>905269</v>
+      </c>
+      <c r="D17" t="n">
         <v>657836</v>
       </c>
-      <c r="R4" t="n">
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="n">
+        <v>961677</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1036809</v>
+      </c>
+      <c r="D18" t="n">
         <v>833997</v>
       </c>
-      <c r="S4" t="n">
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1076557</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1145363</v>
+      </c>
+      <c r="D19" t="n">
         <v>955939</v>
       </c>
-      <c r="T4" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1064808</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1100058</v>
+      </c>
+      <c r="D20" t="n">
         <v>999615</v>
       </c>
-      <c r="U4" t="n">
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>966197</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1003893</v>
+      </c>
+      <c r="D21" t="n">
         <v>889681</v>
       </c>
-      <c r="V4" t="n">
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1092384</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1150764</v>
+      </c>
+      <c r="D22" t="n">
         <v>986406</v>
       </c>
-      <c r="W4" t="n">
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1240731</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1320376</v>
+      </c>
+      <c r="D23" t="n">
         <v>1096030</v>
       </c>
-      <c r="X4" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1416640</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1476833</v>
+      </c>
+      <c r="D24" t="n">
         <v>1299329</v>
       </c>
-      <c r="Y4" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1519398</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1610308</v>
+      </c>
+      <c r="D25" t="n">
         <v>1344028</v>
       </c>
-      <c r="Z4" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1499180</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1545828</v>
+      </c>
+      <c r="D26" t="n">
         <v>1410755</v>
       </c>
-      <c r="AA4" t="n">
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1851637</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1935522</v>
+      </c>
+      <c r="D27" t="n">
         <v>1687923</v>
       </c>
-      <c r="AB4" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2196615</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2314620</v>
+      </c>
+      <c r="D28" t="n">
         <v>1933596</v>
       </c>
-      <c r="AC4" t="n">
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2638159</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2824079</v>
+      </c>
+      <c r="D29" t="n">
         <v>2245940</v>
       </c>
-      <c r="AD4" t="n">
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3141317</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3326146</v>
+      </c>
+      <c r="D30" t="n">
         <v>2737181</v>
       </c>
     </row>
